--- a/site-data.xlsx
+++ b/site-data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\mc-website-github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8269B7B6-6D25-457F-BB4E-9A06A4D2EB1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6778DA4-A25C-431D-AEA0-319992BFB575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="143">
   <si>
     <t>M&amp;C Website – Content Sheet</t>
   </si>
@@ -450,9 +450,6 @@
   </si>
   <si>
     <t>For rent</t>
-  </si>
-  <si>
-    <t>Rent- 110000   Sale 15.5M</t>
   </si>
   <si>
     <t>https://www.instagram.com/reel/Dbk5nkGt5hp/</t>
@@ -1135,7 +1132,7 @@
         <v>49</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>50</v>
@@ -1196,8 +1193,8 @@
       <c r="E4" s="5">
         <v>3</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>142</v>
+      <c r="F4" s="5">
+        <v>110000</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>139</v>

--- a/site-data.xlsx
+++ b/site-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\mc-website-github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6778DA4-A25C-431D-AEA0-319992BFB575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ECDE067-52FB-4A2A-A7FD-1DEA8E74C17C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Read Me First" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="145">
   <si>
     <t>M&amp;C Website – Content Sheet</t>
   </si>
@@ -443,9 +443,6 @@
     <t>3 Bedroom Apartment, Mi Vida, Garden City</t>
   </si>
   <si>
-    <t>For Sale and Rent</t>
-  </si>
-  <si>
     <t>For Rent</t>
   </si>
   <si>
@@ -453,6 +450,15 @@
   </si>
   <si>
     <t>https://www.instagram.com/reel/Dbk5nkGt5hp/</t>
+  </si>
+  <si>
+    <t>For  Rent</t>
+  </si>
+  <si>
+    <t>15.5M</t>
+  </si>
+  <si>
+    <t>For  Sale</t>
   </si>
 </sst>
 </file>
@@ -1039,7 +1045,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1117,7 +1123,7 @@
         <v>140000</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>46</v>
@@ -1132,7 +1138,7 @@
         <v>49</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>50</v>
@@ -1158,7 +1164,7 @@
         <v>89000</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>51</v>
@@ -1197,7 +1203,7 @@
         <v>110000</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>55</v>
@@ -1211,6 +1217,41 @@
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2</v>
+      </c>
+      <c r="E5" s="5">
+        <v>3</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" s="5" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1224,7 +1265,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1912,6 +1953,248 @@
         <v>117</v>
       </c>
       <c r="D56" s="5"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="5">
+        <v>4</v>
+      </c>
+      <c r="B57" s="5">
+        <v>1</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="5">
+        <v>4</v>
+      </c>
+      <c r="B58" s="5">
+        <v>2</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D58" s="5"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="5">
+        <v>4</v>
+      </c>
+      <c r="B59" s="5">
+        <v>3</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D59" s="5"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="5">
+        <v>4</v>
+      </c>
+      <c r="B60" s="5">
+        <v>4</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D60" s="5"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="5">
+        <v>4</v>
+      </c>
+      <c r="B61" s="5">
+        <v>5</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D61" s="5"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" s="5">
+        <v>4</v>
+      </c>
+      <c r="B62" s="5">
+        <v>6</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D62" s="5"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" s="5">
+        <v>4</v>
+      </c>
+      <c r="B63" s="5">
+        <v>7</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D63" s="5"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" s="5">
+        <v>4</v>
+      </c>
+      <c r="B64" s="5">
+        <v>8</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D64" s="5"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" s="5">
+        <v>4</v>
+      </c>
+      <c r="B65" s="5">
+        <v>9</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D65" s="5"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" s="5">
+        <v>4</v>
+      </c>
+      <c r="B66" s="5">
+        <v>10</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D66" s="5"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" s="5">
+        <v>4</v>
+      </c>
+      <c r="B67" s="5">
+        <v>11</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D67" s="5"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" s="5">
+        <v>4</v>
+      </c>
+      <c r="B68" s="5">
+        <v>12</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D68" s="5"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" s="5">
+        <v>4</v>
+      </c>
+      <c r="B69" s="5">
+        <v>13</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D69" s="5"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" s="5">
+        <v>4</v>
+      </c>
+      <c r="B70" s="5">
+        <v>14</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D70" s="5"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" s="5">
+        <v>4</v>
+      </c>
+      <c r="B71" s="5">
+        <v>15</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D71" s="5"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" s="5">
+        <v>4</v>
+      </c>
+      <c r="B72" s="5">
+        <v>16</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D72" s="5"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" s="5">
+        <v>4</v>
+      </c>
+      <c r="B73" s="5">
+        <v>17</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D73" s="5"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" s="5">
+        <v>4</v>
+      </c>
+      <c r="B74" s="5">
+        <v>18</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D74" s="5"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" s="5">
+        <v>4</v>
+      </c>
+      <c r="B75" s="5">
+        <v>19</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D75" s="5"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" s="5">
+        <v>4</v>
+      </c>
+      <c r="B76" s="5">
+        <v>20</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D76" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/site-data.xlsx
+++ b/site-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\mc-website-github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ECDE067-52FB-4A2A-A7FD-1DEA8E74C17C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A72793A-85AE-4537-8AD6-CF954D83C3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Read Me First" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="146">
   <si>
     <t>M&amp;C Website – Content Sheet</t>
   </si>
@@ -459,6 +459,9 @@
   </si>
   <si>
     <t>For  Sale</t>
+  </si>
+  <si>
+    <t>A two bedroom laid out over two floors with three bathrooms, in Mi Vida development off Thika Road. Shown furnished; the rent quoted is for Sale</t>
   </si>
 </sst>
 </file>
@@ -1243,7 +1246,7 @@
         <v>144</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>55</v>
+        <v>145</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>56</v>

--- a/site-data.xlsx
+++ b/site-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\mc-website-github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A72793A-85AE-4537-8AD6-CF954D83C3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE0C535-F9EF-4AFB-ACDA-B0246B806EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="145">
   <si>
     <t>M&amp;C Website – Content Sheet</t>
   </si>
@@ -453,9 +453,6 @@
   </si>
   <si>
     <t>For  Rent</t>
-  </si>
-  <si>
-    <t>15.5M</t>
   </si>
   <si>
     <t>For  Sale</t>
@@ -1239,14 +1236,14 @@
       <c r="E5" s="5">
         <v>3</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="5">
+        <v>15500000</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>144</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>145</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>56</v>
